--- a/backend/data/financials_by_company/1940.HK.xlsx
+++ b/backend/data/financials_by_company/1940.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,59 +662,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-4702955.018014</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.184422</v>
-      </c>
-      <c r="D2" t="n">
-        <v>327188037</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-25501102</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-25501102</v>
-      </c>
-      <c r="G2" t="n">
-        <v>130046644</v>
-      </c>
-      <c r="H2" t="n">
-        <v>121680515</v>
-      </c>
-      <c r="I2" t="n">
-        <v>998364935</v>
-      </c>
-      <c r="J2" t="n">
-        <v>301686935</v>
-      </c>
-      <c r="K2" t="n">
-        <v>180006420</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-18476622</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20553141</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2076519</v>
-      </c>
-      <c r="O2" t="n">
-        <v>150844790.981986</v>
-      </c>
-      <c r="P2" t="n">
-        <v>130046644</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1110192077</v>
-      </c>
-      <c r="R2" t="n">
-        <v>177929900</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>1200000000</v>
       </c>
@@ -722,144 +688,94 @@
         <v>1200000000</v>
       </c>
       <c r="U2" t="n">
-        <v>0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="V2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="W2" t="n">
-        <v>130046644</v>
-      </c>
-      <c r="X2" t="n">
-        <v>130046644</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>130046644</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>130046644</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>130046644</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>29406635</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>159453279</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-109239</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-25501102</v>
-      </c>
+        <v>-0.02</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
-        <v>-12390334</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>37891436</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-18476622</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>20553141</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2076519</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>203419692</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>111827142</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>3078422</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>66252240</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>49599283</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2318990</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>47280293</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>315246834</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>998364935</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1313611769</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>1313611769</v>
-      </c>
+        <v>363365</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-3120619.187739</v>
+        <v>-2259955.581134</v>
       </c>
       <c r="C3" t="n">
-        <v>0.161611</v>
+        <v>0.299814</v>
       </c>
       <c r="D3" t="n">
-        <v>330044995</v>
+        <v>322378643</v>
       </c>
       <c r="E3" t="n">
-        <v>-19309391</v>
+        <v>-7537864</v>
       </c>
       <c r="F3" t="n">
-        <v>-19309391</v>
+        <v>-7537864</v>
       </c>
       <c r="G3" t="n">
-        <v>128076261</v>
+        <v>112742520</v>
       </c>
       <c r="H3" t="n">
-        <v>132322878</v>
+        <v>126366986</v>
       </c>
       <c r="I3" t="n">
-        <v>1159051046</v>
+        <v>1139793628</v>
       </c>
       <c r="J3" t="n">
-        <v>310735604</v>
+        <v>314840779</v>
       </c>
       <c r="K3" t="n">
-        <v>178412726</v>
+        <v>188473793</v>
       </c>
       <c r="L3" t="n">
-        <v>-21715449</v>
+        <v>-26020054</v>
       </c>
       <c r="M3" t="n">
-        <v>25647919</v>
+        <v>27455883</v>
       </c>
       <c r="N3" t="n">
-        <v>3932470</v>
+        <v>1435829</v>
       </c>
       <c r="O3" t="n">
-        <v>144265032.812261</v>
+        <v>118020428.418866</v>
       </c>
       <c r="P3" t="n">
-        <v>128076261</v>
+        <v>112742520</v>
       </c>
       <c r="Q3" t="n">
-        <v>1298922448</v>
+        <v>1306475615</v>
       </c>
       <c r="R3" t="n">
-        <v>174480256</v>
+        <v>187037964</v>
       </c>
       <c r="S3" t="n">
         <v>1200000000</v>
@@ -868,142 +784,142 @@
         <v>1200000000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="V3" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="W3" t="n">
-        <v>128076261</v>
+        <v>112742520</v>
       </c>
       <c r="X3" t="n">
-        <v>128076261</v>
+        <v>112742520</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>128076261</v>
+        <v>112742520</v>
       </c>
       <c r="AA3" t="n">
-        <v>128076261</v>
+        <v>112742520</v>
       </c>
       <c r="AB3" t="n">
-        <v>128076261</v>
+        <v>112742520</v>
       </c>
       <c r="AC3" t="n">
-        <v>24688546</v>
+        <v>48275390</v>
       </c>
       <c r="AD3" t="n">
-        <v>152764807</v>
+        <v>161017910</v>
       </c>
       <c r="AE3" t="n">
-        <v>-359789</v>
+        <v>-213769</v>
       </c>
       <c r="AF3" t="n">
-        <v>-19309391</v>
+        <v>-7537864</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>19309391</v>
+        <v>7537864</v>
       </c>
       <c r="AI3" t="n">
-        <v>-21715449</v>
+        <v>-26020054</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25647919</v>
+        <v>27455883</v>
       </c>
       <c r="AK3" t="n">
-        <v>3932470</v>
+        <v>1435829</v>
       </c>
       <c r="AL3" t="n">
-        <v>192231540</v>
+        <v>175168626</v>
       </c>
       <c r="AM3" t="n">
-        <v>139871402</v>
+        <v>166681987</v>
       </c>
       <c r="AN3" t="n">
-        <v>15363770</v>
+        <v>8135000</v>
       </c>
       <c r="AO3" t="n">
-        <v>73603329</v>
+        <v>75341624</v>
       </c>
       <c r="AP3" t="n">
-        <v>56284704</v>
+        <v>84179989</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1893235</v>
+        <v>2000851</v>
       </c>
       <c r="AR3" t="n">
-        <v>54391469</v>
+        <v>82179138</v>
       </c>
       <c r="AS3" t="n">
-        <v>332102942</v>
+        <v>341850613</v>
       </c>
       <c r="AT3" t="n">
-        <v>1159051046</v>
+        <v>1139793628</v>
       </c>
       <c r="AU3" t="n">
-        <v>1491153988</v>
+        <v>1481644241</v>
       </c>
       <c r="AV3" t="n">
-        <v>1491153988</v>
+        <v>1481644241</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-2259955.581134</v>
+        <v>-3120619.187739</v>
       </c>
       <c r="C4" t="n">
-        <v>0.299814</v>
+        <v>0.161611</v>
       </c>
       <c r="D4" t="n">
-        <v>322378643</v>
+        <v>330044995</v>
       </c>
       <c r="E4" t="n">
-        <v>-7537864</v>
+        <v>-19309391</v>
       </c>
       <c r="F4" t="n">
-        <v>-7537864</v>
+        <v>-19309391</v>
       </c>
       <c r="G4" t="n">
-        <v>112742520</v>
+        <v>128076261</v>
       </c>
       <c r="H4" t="n">
-        <v>126366986</v>
+        <v>132322878</v>
       </c>
       <c r="I4" t="n">
-        <v>1139793628</v>
+        <v>1159051046</v>
       </c>
       <c r="J4" t="n">
-        <v>314840779</v>
+        <v>310735604</v>
       </c>
       <c r="K4" t="n">
-        <v>188473793</v>
+        <v>178412726</v>
       </c>
       <c r="L4" t="n">
-        <v>-26020054</v>
+        <v>-21715449</v>
       </c>
       <c r="M4" t="n">
-        <v>27455883</v>
+        <v>25647919</v>
       </c>
       <c r="N4" t="n">
-        <v>1435829</v>
+        <v>3932470</v>
       </c>
       <c r="O4" t="n">
-        <v>118020428.418866</v>
+        <v>144265032.812261</v>
       </c>
       <c r="P4" t="n">
-        <v>112742520</v>
+        <v>128076261</v>
       </c>
       <c r="Q4" t="n">
-        <v>1306475615</v>
+        <v>1298922448</v>
       </c>
       <c r="R4" t="n">
-        <v>187037964</v>
+        <v>174480256</v>
       </c>
       <c r="S4" t="n">
         <v>1200000000</v>
@@ -1012,142 +928,142 @@
         <v>1200000000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="W4" t="n">
-        <v>112742520</v>
+        <v>128076261</v>
       </c>
       <c r="X4" t="n">
-        <v>112742520</v>
+        <v>128076261</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>112742520</v>
+        <v>128076261</v>
       </c>
       <c r="AA4" t="n">
-        <v>112742520</v>
+        <v>128076261</v>
       </c>
       <c r="AB4" t="n">
-        <v>112742520</v>
+        <v>128076261</v>
       </c>
       <c r="AC4" t="n">
-        <v>48275390</v>
+        <v>24688546</v>
       </c>
       <c r="AD4" t="n">
-        <v>161017910</v>
+        <v>152764807</v>
       </c>
       <c r="AE4" t="n">
-        <v>-213769</v>
+        <v>-359789</v>
       </c>
       <c r="AF4" t="n">
-        <v>-7537864</v>
+        <v>-19309391</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>7537864</v>
+        <v>19309391</v>
       </c>
       <c r="AI4" t="n">
-        <v>-26020054</v>
+        <v>-21715449</v>
       </c>
       <c r="AJ4" t="n">
-        <v>27455883</v>
+        <v>25647919</v>
       </c>
       <c r="AK4" t="n">
-        <v>1435829</v>
+        <v>3932470</v>
       </c>
       <c r="AL4" t="n">
-        <v>175168626</v>
+        <v>192231540</v>
       </c>
       <c r="AM4" t="n">
-        <v>166681987</v>
+        <v>139871402</v>
       </c>
       <c r="AN4" t="n">
-        <v>8135000</v>
+        <v>15363770</v>
       </c>
       <c r="AO4" t="n">
-        <v>75341624</v>
+        <v>73603329</v>
       </c>
       <c r="AP4" t="n">
-        <v>84179989</v>
+        <v>56284704</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2000851</v>
+        <v>1893235</v>
       </c>
       <c r="AR4" t="n">
-        <v>82179138</v>
+        <v>54391469</v>
       </c>
       <c r="AS4" t="n">
-        <v>341850613</v>
+        <v>332102942</v>
       </c>
       <c r="AT4" t="n">
-        <v>1139793628</v>
+        <v>1159051046</v>
       </c>
       <c r="AU4" t="n">
-        <v>1481644241</v>
+        <v>1491153988</v>
       </c>
       <c r="AV4" t="n">
-        <v>1481644241</v>
+        <v>1491153988</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-90841.25</v>
+        <v>-4702955.018014</v>
       </c>
       <c r="C5" t="n">
-        <v>0.25</v>
+        <v>0.184422</v>
       </c>
       <c r="D5" t="n">
-        <v>161317993</v>
+        <v>327188036</v>
       </c>
       <c r="E5" t="n">
-        <v>-363365</v>
+        <v>-25501102</v>
       </c>
       <c r="F5" t="n">
-        <v>-363365</v>
+        <v>-25501102</v>
       </c>
       <c r="G5" t="n">
-        <v>-26816529</v>
+        <v>130046644</v>
       </c>
       <c r="H5" t="n">
-        <v>116994585</v>
+        <v>121680515</v>
       </c>
       <c r="I5" t="n">
-        <v>961131742</v>
+        <v>998364935</v>
       </c>
       <c r="J5" t="n">
-        <v>160954628</v>
+        <v>301686934</v>
       </c>
       <c r="K5" t="n">
-        <v>43960043</v>
+        <v>180006419</v>
       </c>
       <c r="L5" t="n">
-        <v>-28048230</v>
+        <v>-18476621</v>
       </c>
       <c r="M5" t="n">
-        <v>29842022</v>
+        <v>20553140</v>
       </c>
       <c r="N5" t="n">
-        <v>1793792</v>
+        <v>2076519</v>
       </c>
       <c r="O5" t="n">
-        <v>-26544005.25</v>
+        <v>150844790.981986</v>
       </c>
       <c r="P5" t="n">
-        <v>-26816529</v>
+        <v>130046644</v>
       </c>
       <c r="Q5" t="n">
-        <v>1165639760</v>
+        <v>1110192077</v>
       </c>
       <c r="R5" t="n">
-        <v>42166251</v>
+        <v>177929900</v>
       </c>
       <c r="S5" t="n">
         <v>1200000000</v>
@@ -1156,88 +1072,226 @@
         <v>1200000000</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="W5" t="n">
-        <v>-26816529</v>
+        <v>130046644</v>
       </c>
       <c r="X5" t="n">
-        <v>-26816529</v>
+        <v>130046644</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-26816529</v>
+        <v>130046644</v>
       </c>
       <c r="AA5" t="n">
-        <v>-26816529</v>
+        <v>130046644</v>
       </c>
       <c r="AB5" t="n">
-        <v>-26816529</v>
+        <v>130046644</v>
       </c>
       <c r="AC5" t="n">
-        <v>40934550</v>
+        <v>29406635</v>
       </c>
       <c r="AD5" t="n">
-        <v>14118021</v>
+        <v>159453279</v>
       </c>
       <c r="AE5" t="n">
-        <v>-693821</v>
+        <v>-109239</v>
       </c>
       <c r="AF5" t="n">
-        <v>-363365</v>
+        <v>-25501102</v>
       </c>
       <c r="AG5" t="n">
-        <v>363365</v>
+        <v>-12390334</v>
       </c>
       <c r="AH5" t="n">
+        <v>37891436</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-18476621</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>20553140</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2076519</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>203419692</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>111827142</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>3078422</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>66252240</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>49599283</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2318990</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>47280293</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>315246834</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>998364935</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1313611769</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1313611769</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-10375025.08201</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.225591</v>
+      </c>
+      <c r="D6" t="n">
+        <v>382320872</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-45990460</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-45990460</v>
+      </c>
+      <c r="G6" t="n">
+        <v>156266337</v>
+      </c>
+      <c r="H6" t="n">
+        <v>119647768</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1150164605</v>
+      </c>
+      <c r="J6" t="n">
+        <v>336330412</v>
+      </c>
+      <c r="K6" t="n">
+        <v>216682644</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-12923017</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14894831</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1971814</v>
+      </c>
+      <c r="O6" t="n">
+        <v>191881771.91799</v>
+      </c>
+      <c r="P6" t="n">
+        <v>156266337</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1268326337</v>
+      </c>
+      <c r="R6" t="n">
+        <v>214710830</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>156266337</v>
+      </c>
+      <c r="X6" t="n">
+        <v>156266337</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0</v>
       </c>
-      <c r="AI5" t="n">
-        <v>-28048230</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>29842022</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1793792</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>43631115</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>204508018</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>66400000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>51503611</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>97422622</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1866961</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>95555661</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>248139133</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>961131742</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1209270875</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1209270875</v>
+      <c r="Z6" t="n">
+        <v>156266337</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>156266337</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>156266337</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>45521476</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>201787813</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-18282</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-45990460</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4328020</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>41662440</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-12923017</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>14894831</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1971814</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>260790157</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>118161732</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7504243</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>81203296</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>43998946</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2575393</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>41423553</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>378951889</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1150164605</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1529116494</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1529116494</v>
       </c>
     </row>
   </sheetData>
@@ -1251,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK5"/>
+  <dimension ref="A1:BK6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,194 +1622,82 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1200000000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1200000000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>276427140</v>
-      </c>
-      <c r="E2" t="n">
-        <v>463694521</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1604702240</v>
-      </c>
-      <c r="G2" t="n">
-        <v>2104216119</v>
-      </c>
-      <c r="H2" t="n">
-        <v>292635835</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1604702240</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3382628</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1643904226</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1844012243</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1643904226</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1643904226</v>
-      </c>
-      <c r="O2" t="n">
-        <v>282372286</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1144391968</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>836016</v>
-      </c>
-      <c r="R2" t="n">
-        <v>836016</v>
-      </c>
-      <c r="S2" t="n">
-        <v>799244521</v>
-      </c>
-      <c r="T2" t="n">
-        <v>252566014</v>
-      </c>
-      <c r="U2" t="n">
-        <v>51203287</v>
-      </c>
-      <c r="V2" t="n">
-        <v>201362727</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1254710</v>
-      </c>
-      <c r="X2" t="n">
-        <v>200108017</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>546678507</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>262331794</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2127918</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>260203876</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>268720172</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>78398573</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>50671500</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>5993277</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>133656822</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2443148747</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1603834405</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4161589</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>39201986</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>39201986</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1560470830</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-1109442642</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2669913472</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>317152649</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>65830859</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2075825987</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>211103977</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>839314342</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10767015</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6510260</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>7043992</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
-      <c r="BA2" t="n">
-        <v>6510260</v>
-      </c>
+      <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>96254620</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>9131493</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>532766201</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-26577192</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>559343393</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>183884753</v>
-      </c>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="n">
-        <v>183884753</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>183884753</v>
-      </c>
+        <v>3133183</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="n">
+        <v>23443760</v>
+      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>1200000000</v>
@@ -1764,40 +1706,40 @@
         <v>1200000000</v>
       </c>
       <c r="D3" t="n">
-        <v>330382357</v>
+        <v>211791654</v>
       </c>
       <c r="E3" t="n">
-        <v>537788025</v>
+        <v>585793492</v>
       </c>
       <c r="F3" t="n">
-        <v>1473351069</v>
+        <v>1344876643</v>
       </c>
       <c r="G3" t="n">
-        <v>2046430270</v>
+        <v>1958363178</v>
       </c>
       <c r="H3" t="n">
-        <v>184621820</v>
+        <v>130305083</v>
       </c>
       <c r="I3" t="n">
-        <v>1473351069</v>
+        <v>1344876643</v>
       </c>
       <c r="J3" t="n">
-        <v>4788025</v>
+        <v>13263373</v>
       </c>
       <c r="K3" t="n">
-        <v>1513430270</v>
+        <v>1385833059</v>
       </c>
       <c r="L3" t="n">
-        <v>1759430270</v>
+        <v>1716603178</v>
       </c>
       <c r="M3" t="n">
-        <v>1513430270</v>
+        <v>1385833059</v>
       </c>
       <c r="N3" t="n">
-        <v>1513430270</v>
+        <v>1385833059</v>
       </c>
       <c r="O3" t="n">
-        <v>167458543</v>
+        <v>55692208</v>
       </c>
       <c r="P3" t="n">
         <v>1144391968</v>
@@ -1809,140 +1751,144 @@
         <v>836016</v>
       </c>
       <c r="S3" t="n">
-        <v>959531042</v>
+        <v>1220843385</v>
       </c>
       <c r="T3" t="n">
-        <v>291293550</v>
+        <v>360357987</v>
       </c>
       <c r="U3" t="n">
-        <v>42633676</v>
+        <v>27158986</v>
       </c>
       <c r="V3" t="n">
-        <v>248659874</v>
+        <v>333199001</v>
       </c>
       <c r="W3" t="n">
-        <v>2659874</v>
+        <v>2428882</v>
       </c>
       <c r="X3" t="n">
-        <v>246000000</v>
+        <v>330770119</v>
       </c>
       <c r="Y3" t="n">
-        <v>668237492</v>
+        <v>860485398</v>
       </c>
       <c r="Z3" t="n">
-        <v>289128151</v>
+        <v>252594491</v>
       </c>
       <c r="AA3" t="n">
-        <v>2128151</v>
+        <v>10834491</v>
       </c>
       <c r="AB3" t="n">
-        <v>287000000</v>
+        <v>241760000</v>
       </c>
       <c r="AC3" t="n">
-        <v>372884259</v>
+        <v>599037101</v>
       </c>
       <c r="AD3" t="n">
-        <v>89037830</v>
+        <v>101134594</v>
       </c>
       <c r="AE3" t="n">
-        <v>50671500</v>
+        <v>100671500</v>
       </c>
       <c r="AF3" t="n">
-        <v>5293703</v>
+        <v>15550185</v>
       </c>
       <c r="AG3" t="n">
-        <v>227881226</v>
+        <v>381680822</v>
       </c>
       <c r="AH3" t="n">
-        <v>2472961312</v>
+        <v>2606676444</v>
       </c>
       <c r="AI3" t="n">
-        <v>1620102000</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>1615885963</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>8432808</v>
+      </c>
       <c r="AK3" t="n">
-        <v>173994</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>4956487</v>
+        <v>3304108</v>
       </c>
       <c r="AM3" t="n">
-        <v>40079201</v>
+        <v>40956416</v>
       </c>
       <c r="AN3" t="n">
-        <v>40079201</v>
+        <v>40956416</v>
       </c>
       <c r="AO3" t="n">
-        <v>1574892318</v>
+        <v>1571625439</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1324734661</v>
+        <v>-1175052863</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2899626979</v>
+        <v>2746678302</v>
       </c>
       <c r="AR3" t="n">
-        <v>204907140</v>
+        <v>93308896</v>
       </c>
       <c r="AS3" t="n">
-        <v>70051992</v>
+        <v>69657922</v>
       </c>
       <c r="AT3" t="n">
-        <v>2351712262</v>
+        <v>2311543913</v>
       </c>
       <c r="AU3" t="n">
-        <v>272955585</v>
+        <v>272167571</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>852859312</v>
+        <v>990790481</v>
       </c>
       <c r="AX3" t="n">
-        <v>11846484</v>
+        <v>11606232</v>
       </c>
       <c r="AY3" t="n">
-        <v>9709236</v>
+        <v>11635569</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>6305811</v>
+        <v>9181456</v>
       </c>
       <c r="BB3" t="n">
-        <v>3403425</v>
+        <v>2454113</v>
       </c>
       <c r="BC3" t="n">
-        <v>80440328</v>
+        <v>29583821</v>
       </c>
       <c r="BD3" t="n">
-        <v>4327575</v>
+        <v>10190850</v>
       </c>
       <c r="BE3" t="n">
-        <v>543918046</v>
+        <v>567035544</v>
       </c>
       <c r="BF3" t="n">
-        <v>-23498770</v>
+        <v>-8135000</v>
       </c>
       <c r="BG3" t="n">
-        <v>567416816</v>
+        <v>575170544</v>
       </c>
       <c r="BH3" t="n">
-        <v>202617643</v>
-      </c>
-      <c r="BI3" t="inlineStr"/>
+        <v>360738465</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>28812893</v>
+      </c>
       <c r="BJ3" t="n">
-        <v>202617643</v>
+        <v>360738465</v>
       </c>
       <c r="BK3" t="n">
-        <v>202617643</v>
+        <v>360738465</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>1200000000</v>
@@ -1951,40 +1897,40 @@
         <v>1200000000</v>
       </c>
       <c r="D4" t="n">
-        <v>211791654</v>
+        <v>330382357</v>
       </c>
       <c r="E4" t="n">
-        <v>585793492</v>
+        <v>537788025</v>
       </c>
       <c r="F4" t="n">
-        <v>1344876643</v>
+        <v>1473351069</v>
       </c>
       <c r="G4" t="n">
-        <v>1958363178</v>
+        <v>2046430270</v>
       </c>
       <c r="H4" t="n">
-        <v>130305083</v>
+        <v>184621820</v>
       </c>
       <c r="I4" t="n">
-        <v>1344876643</v>
+        <v>1473351069</v>
       </c>
       <c r="J4" t="n">
-        <v>13263373</v>
+        <v>4788025</v>
       </c>
       <c r="K4" t="n">
-        <v>1385833059</v>
+        <v>1513430270</v>
       </c>
       <c r="L4" t="n">
-        <v>1716603178</v>
+        <v>1759430270</v>
       </c>
       <c r="M4" t="n">
-        <v>1385833059</v>
+        <v>1513430270</v>
       </c>
       <c r="N4" t="n">
-        <v>1385833059</v>
+        <v>1513430270</v>
       </c>
       <c r="O4" t="n">
-        <v>55692208</v>
+        <v>167458543</v>
       </c>
       <c r="P4" t="n">
         <v>1144391968</v>
@@ -1996,144 +1942,140 @@
         <v>836016</v>
       </c>
       <c r="S4" t="n">
-        <v>1220843385</v>
+        <v>959531042</v>
       </c>
       <c r="T4" t="n">
-        <v>360357987</v>
+        <v>291293550</v>
       </c>
       <c r="U4" t="n">
-        <v>27158986</v>
+        <v>42633676</v>
       </c>
       <c r="V4" t="n">
-        <v>333199001</v>
+        <v>248659874</v>
       </c>
       <c r="W4" t="n">
-        <v>2428882</v>
+        <v>2659874</v>
       </c>
       <c r="X4" t="n">
-        <v>330770119</v>
+        <v>246000000</v>
       </c>
       <c r="Y4" t="n">
-        <v>860485398</v>
+        <v>668237492</v>
       </c>
       <c r="Z4" t="n">
-        <v>252594491</v>
+        <v>289128151</v>
       </c>
       <c r="AA4" t="n">
-        <v>10834491</v>
+        <v>2128151</v>
       </c>
       <c r="AB4" t="n">
-        <v>241760000</v>
+        <v>287000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>599037101</v>
+        <v>372884259</v>
       </c>
       <c r="AD4" t="n">
-        <v>101134594</v>
+        <v>89037830</v>
       </c>
       <c r="AE4" t="n">
-        <v>100671500</v>
+        <v>50671500</v>
       </c>
       <c r="AF4" t="n">
-        <v>15550185</v>
+        <v>5293703</v>
       </c>
       <c r="AG4" t="n">
-        <v>381680822</v>
+        <v>227881226</v>
       </c>
       <c r="AH4" t="n">
-        <v>2606676444</v>
+        <v>2472961312</v>
       </c>
       <c r="AI4" t="n">
-        <v>1615885963</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>8432808</v>
-      </c>
+        <v>1620102000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>173994</v>
       </c>
       <c r="AL4" t="n">
-        <v>3304108</v>
+        <v>4956487</v>
       </c>
       <c r="AM4" t="n">
-        <v>40956416</v>
+        <v>40079201</v>
       </c>
       <c r="AN4" t="n">
-        <v>40956416</v>
+        <v>40079201</v>
       </c>
       <c r="AO4" t="n">
-        <v>1571625439</v>
+        <v>1574892318</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1175052863</v>
+        <v>-1324734661</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2746678302</v>
+        <v>2899626979</v>
       </c>
       <c r="AR4" t="n">
-        <v>93308896</v>
+        <v>204907140</v>
       </c>
       <c r="AS4" t="n">
-        <v>69657922</v>
+        <v>70051992</v>
       </c>
       <c r="AT4" t="n">
-        <v>2311543913</v>
+        <v>2351712262</v>
       </c>
       <c r="AU4" t="n">
-        <v>272167571</v>
+        <v>272955585</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>990790481</v>
+        <v>852859312</v>
       </c>
       <c r="AX4" t="n">
-        <v>11606232</v>
+        <v>11846484</v>
       </c>
       <c r="AY4" t="n">
-        <v>11635569</v>
+        <v>9709236</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>9181456</v>
+        <v>6305811</v>
       </c>
       <c r="BB4" t="n">
-        <v>2454113</v>
+        <v>3403425</v>
       </c>
       <c r="BC4" t="n">
-        <v>29583821</v>
+        <v>80440328</v>
       </c>
       <c r="BD4" t="n">
-        <v>10190850</v>
+        <v>4327575</v>
       </c>
       <c r="BE4" t="n">
-        <v>567035544</v>
+        <v>543918046</v>
       </c>
       <c r="BF4" t="n">
-        <v>-8135000</v>
+        <v>-23498770</v>
       </c>
       <c r="BG4" t="n">
-        <v>575170544</v>
+        <v>567416816</v>
       </c>
       <c r="BH4" t="n">
-        <v>360738465</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>28812893</v>
-      </c>
+        <v>202617643</v>
+      </c>
+      <c r="BI4" t="inlineStr"/>
       <c r="BJ4" t="n">
-        <v>360738465</v>
+        <v>202617643</v>
       </c>
       <c r="BK4" t="n">
-        <v>360738465</v>
+        <v>202617643</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>1200000000</v>
@@ -2142,40 +2084,40 @@
         <v>1200000000</v>
       </c>
       <c r="D5" t="n">
-        <v>304163683</v>
+        <v>276427140</v>
       </c>
       <c r="E5" t="n">
-        <v>615438670</v>
+        <v>463694521</v>
       </c>
       <c r="F5" t="n">
-        <v>1239926891</v>
+        <v>1604702240</v>
       </c>
       <c r="G5" t="n">
-        <v>1883746171</v>
+        <v>2104216119</v>
       </c>
       <c r="H5" t="n">
-        <v>22484536</v>
+        <v>292635835</v>
       </c>
       <c r="I5" t="n">
-        <v>1239926891</v>
+        <v>1604702240</v>
       </c>
       <c r="J5" t="n">
-        <v>13722369</v>
+        <v>3382628</v>
       </c>
       <c r="K5" t="n">
-        <v>1282029870</v>
+        <v>1643904226</v>
       </c>
       <c r="L5" t="n">
-        <v>1595236171</v>
+        <v>1844012243</v>
       </c>
       <c r="M5" t="n">
-        <v>1282029870</v>
+        <v>1643904226</v>
       </c>
       <c r="N5" t="n">
-        <v>1282029870</v>
+        <v>1643904226</v>
       </c>
       <c r="O5" t="n">
-        <v>-42404801</v>
+        <v>282372286</v>
       </c>
       <c r="P5" t="n">
         <v>1144391968</v>
@@ -2187,137 +2129,316 @@
         <v>836016</v>
       </c>
       <c r="S5" t="n">
-        <v>1124019307</v>
+        <v>799244521</v>
       </c>
       <c r="T5" t="n">
-        <v>336186920</v>
+        <v>252566014</v>
       </c>
       <c r="U5" t="n">
-        <v>19785267</v>
+        <v>51203287</v>
       </c>
       <c r="V5" t="n">
-        <v>316401653</v>
+        <v>201362727</v>
       </c>
       <c r="W5" t="n">
-        <v>3195352</v>
+        <v>1254710</v>
       </c>
       <c r="X5" t="n">
-        <v>313206301</v>
+        <v>200108017</v>
       </c>
       <c r="Y5" t="n">
-        <v>787832387</v>
+        <v>546678507</v>
       </c>
       <c r="Z5" t="n">
-        <v>299037017</v>
+        <v>262331794</v>
       </c>
       <c r="AA5" t="n">
-        <v>10527017</v>
+        <v>2127918</v>
       </c>
       <c r="AB5" t="n">
-        <v>288510000</v>
+        <v>260203876</v>
       </c>
       <c r="AC5" t="n">
-        <v>479450492</v>
+        <v>268720172</v>
       </c>
       <c r="AD5" t="n">
-        <v>118655847</v>
+        <v>78398573</v>
       </c>
       <c r="AE5" t="n">
-        <v>100671500</v>
+        <v>50671500</v>
       </c>
       <c r="AF5" t="n">
-        <v>12838721</v>
+        <v>5993277</v>
       </c>
       <c r="AG5" t="n">
-        <v>247284424</v>
+        <v>133656822</v>
       </c>
       <c r="AH5" t="n">
-        <v>2406049177</v>
+        <v>2443148747</v>
       </c>
       <c r="AI5" t="n">
-        <v>1595732254</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>7043992</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>1603834405</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
       <c r="AL5" t="n">
-        <v>2037083</v>
+        <v>4161589</v>
       </c>
       <c r="AM5" t="n">
-        <v>42102979</v>
+        <v>39201986</v>
       </c>
       <c r="AN5" t="n">
-        <v>42102979</v>
+        <v>39201986</v>
       </c>
       <c r="AO5" t="n">
-        <v>1551592192</v>
+        <v>1560470830</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1082232641</v>
+        <v>-1109442642</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2633824833</v>
+        <v>2669913472</v>
       </c>
       <c r="AR5" t="n">
-        <v>21209257</v>
+        <v>317152649</v>
       </c>
       <c r="AS5" t="n">
-        <v>67759144</v>
+        <v>65830859</v>
       </c>
       <c r="AT5" t="n">
-        <v>2251894842</v>
+        <v>2075825987</v>
       </c>
       <c r="AU5" t="n">
-        <v>292961590</v>
+        <v>211103977</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>810316923</v>
+        <v>839314342</v>
       </c>
       <c r="AX5" t="n">
-        <v>10656604</v>
+        <v>10767015</v>
       </c>
       <c r="AY5" t="n">
-        <v>10146550</v>
+        <v>6510260</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>7013367</v>
+        <v>6510260</v>
       </c>
       <c r="BB5" t="n">
-        <v>3133183</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>25487913</v>
+        <v>96254620</v>
       </c>
       <c r="BD5" t="n">
-        <v>39262715</v>
+        <v>9131493</v>
       </c>
       <c r="BE5" t="n">
-        <v>427210523</v>
+        <v>532766201</v>
       </c>
       <c r="BF5" t="n">
+        <v>-26577192</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>559343393</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>183884753</v>
+      </c>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="n">
+        <v>183884753</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>183884753</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1200000000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>124761990</v>
+      </c>
+      <c r="E6" t="n">
+        <v>276732214</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1757896264</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2071021567</v>
+      </c>
+      <c r="H6" t="n">
+        <v>494376066</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1757896264</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1931682</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1796221035</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1958067578</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1796221035</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1796221035</v>
+      </c>
+      <c r="O6" t="n">
+        <v>420570396</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1144391968</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>836016</v>
+      </c>
+      <c r="R6" t="n">
+        <v>836016</v>
+      </c>
+      <c r="S6" t="n">
+        <v>651826922</v>
+      </c>
+      <c r="T6" t="n">
+        <v>230324707</v>
+      </c>
+      <c r="U6" t="n">
+        <v>68313015</v>
+      </c>
+      <c r="V6" t="n">
+        <v>162011692</v>
+      </c>
+      <c r="W6" t="n">
+        <v>165149</v>
+      </c>
+      <c r="X6" t="n">
+        <v>161846543</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>421502215</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>114720522</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1766533</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>112953989</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>295678238</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>33381726</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>50671500</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>28455557</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>183169455</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2448047957</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1532169676</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>11484617</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>38324771</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>38324771</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1482360288</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-1191406043</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2673766331</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>123393819</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>38587293</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2270126927</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>241658292</v>
+      </c>
+      <c r="AV6" t="n">
         <v>0</v>
       </c>
-      <c r="BG5" t="n">
-        <v>427210523</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>297552618</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>23443760</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>297552618</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>297552618</v>
+      <c r="AW6" t="n">
+        <v>915878281</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>13658399</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6528456</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>6528456</v>
+      </c>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="n">
+        <v>82726657</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>12282007</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>650644220</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-34081435</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>684725655</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>150038542</v>
+      </c>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>150038542</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>150038542</v>
       </c>
     </row>
   </sheetData>
@@ -2331,7 +2452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM5"/>
+  <dimension ref="A1:AM6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2528,460 +2649,503 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>24259159</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-287000000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>210000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-152353577</v>
-      </c>
-      <c r="F2" t="n">
-        <v>183884753</v>
-      </c>
-      <c r="G2" t="n">
-        <v>202617643</v>
-      </c>
-      <c r="H2" t="n">
-        <v>530452</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-19263342</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-77974128</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>-148771500</v>
+      </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-77000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-77000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-287000000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>210000000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-117901950</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="n">
-        <v>-117901950</v>
-      </c>
-      <c r="U2" t="n">
-        <v>34451627</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-152353577</v>
-      </c>
-      <c r="W2" t="n">
-        <v>176612736</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-19646077</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-21695280</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-112651602</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-17580471</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-103269963</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="n">
-        <v>725409</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>7473423</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>18476621</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>3078422</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>121680515</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>121680515</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>-120549</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-9854029</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>159453279</v>
-      </c>
+        <v>-148771500</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>-66400000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-66400000</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="n">
+        <v>72784666</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>612573</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-67971020</v>
+        <v>82544375</v>
       </c>
       <c r="C3" t="n">
-        <v>-399530119</v>
+        <v>-510020000</v>
       </c>
       <c r="D3" t="n">
-        <v>360000000</v>
+        <v>480833818</v>
       </c>
       <c r="E3" t="n">
-        <v>-69378570</v>
+        <v>-114563260</v>
       </c>
       <c r="F3" t="n">
-        <v>202617643</v>
+        <v>360738465</v>
       </c>
       <c r="G3" t="n">
-        <v>360738465</v>
+        <v>297552618</v>
       </c>
       <c r="H3" t="n">
-        <v>-137126</v>
+        <v>10516419</v>
       </c>
       <c r="I3" t="n">
-        <v>-157983696</v>
+        <v>52669428</v>
       </c>
       <c r="J3" t="n">
-        <v>-90012676</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-50000000</v>
-      </c>
+        <v>-29874947</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-50000000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-39530119</v>
+        <v>-29186182</v>
       </c>
       <c r="N3" t="n">
-        <v>-39530119</v>
+        <v>-29186182</v>
       </c>
       <c r="O3" t="n">
-        <v>-399530119</v>
+        <v>-510020000</v>
       </c>
       <c r="P3" t="n">
-        <v>360000000</v>
+        <v>480833818</v>
       </c>
       <c r="Q3" t="n">
-        <v>-69378570</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+        <v>-114563260</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
       <c r="T3" t="n">
-        <v>-69378570</v>
+        <v>-114563260</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-69378570</v>
+        <v>-114563260</v>
       </c>
       <c r="W3" t="n">
-        <v>1407550</v>
+        <v>197107635</v>
       </c>
       <c r="X3" t="n">
-        <v>-23749273</v>
+        <v>-36289111</v>
       </c>
       <c r="Y3" t="n">
-        <v>-29130958</v>
+        <v>-30000232</v>
       </c>
       <c r="Z3" t="n">
-        <v>-286646042</v>
+        <v>-46843202</v>
       </c>
       <c r="AA3" t="n">
-        <v>-104885342</v>
+        <v>19095213</v>
       </c>
       <c r="AB3" t="n">
-        <v>-55463936</v>
-      </c>
-      <c r="AC3" t="inlineStr"/>
+        <v>83510625</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>24955419</v>
+      </c>
       <c r="AD3" t="n">
-        <v>1926333</v>
+        <v>-1489019</v>
       </c>
       <c r="AE3" t="n">
-        <v>-128223097</v>
+        <v>-147960021</v>
       </c>
       <c r="AF3" t="n">
-        <v>21715449</v>
+        <v>26020054</v>
       </c>
       <c r="AG3" t="n">
-        <v>15363770</v>
+        <v>8135000</v>
       </c>
       <c r="AH3" t="n">
-        <v>132322878</v>
+        <v>126366986</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>269348</v>
       </c>
       <c r="AJ3" t="n">
-        <v>132322878</v>
+        <v>126097638</v>
       </c>
       <c r="AK3" t="n">
-        <v>-542472</v>
+        <v>-18837634</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>152764807</v>
+        <v>161017910</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>82544375</v>
+        <v>-67971020</v>
       </c>
       <c r="C4" t="n">
-        <v>-510020000</v>
+        <v>-399530119</v>
       </c>
       <c r="D4" t="n">
-        <v>480833818</v>
+        <v>360000000</v>
       </c>
       <c r="E4" t="n">
-        <v>-114563260</v>
+        <v>-69378570</v>
       </c>
       <c r="F4" t="n">
+        <v>202617643</v>
+      </c>
+      <c r="G4" t="n">
         <v>360738465</v>
       </c>
-      <c r="G4" t="n">
-        <v>297552618</v>
-      </c>
       <c r="H4" t="n">
-        <v>10516419</v>
+        <v>-137126</v>
       </c>
       <c r="I4" t="n">
-        <v>52669428</v>
+        <v>-157983696</v>
       </c>
       <c r="J4" t="n">
-        <v>-29874947</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>-90012676</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-50000000</v>
+      </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-50000000</v>
       </c>
       <c r="M4" t="n">
-        <v>-29186182</v>
+        <v>-39530119</v>
       </c>
       <c r="N4" t="n">
-        <v>-29186182</v>
+        <v>-39530119</v>
       </c>
       <c r="O4" t="n">
-        <v>-510020000</v>
+        <v>-399530119</v>
       </c>
       <c r="P4" t="n">
-        <v>480833818</v>
+        <v>360000000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-114563260</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
+        <v>-69378570</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>-114563260</v>
+        <v>-69378570</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-114563260</v>
+        <v>-69378570</v>
       </c>
       <c r="W4" t="n">
-        <v>197107635</v>
+        <v>1407550</v>
       </c>
       <c r="X4" t="n">
-        <v>-36289111</v>
+        <v>-23749273</v>
       </c>
       <c r="Y4" t="n">
-        <v>-30000232</v>
+        <v>-29130958</v>
       </c>
       <c r="Z4" t="n">
-        <v>-46843202</v>
+        <v>-286646042</v>
       </c>
       <c r="AA4" t="n">
-        <v>19095213</v>
+        <v>-104885342</v>
       </c>
       <c r="AB4" t="n">
-        <v>83510625</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>24955419</v>
-      </c>
+        <v>-55463936</v>
+      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-1489019</v>
+        <v>1926333</v>
       </c>
       <c r="AE4" t="n">
-        <v>-147960021</v>
+        <v>-128223097</v>
       </c>
       <c r="AF4" t="n">
-        <v>26020054</v>
+        <v>21715449</v>
       </c>
       <c r="AG4" t="n">
-        <v>8135000</v>
+        <v>15363770</v>
       </c>
       <c r="AH4" t="n">
-        <v>126366986</v>
+        <v>132322878</v>
       </c>
       <c r="AI4" t="n">
-        <v>269348</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>126097638</v>
+        <v>132322878</v>
       </c>
       <c r="AK4" t="n">
-        <v>-18837634</v>
+        <v>-542472</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>161017910</v>
+        <v>152764807</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>469783</v>
+        <v>24259159</v>
       </c>
       <c r="C5" t="n">
-        <v>-375960000</v>
+        <v>-287000000</v>
       </c>
       <c r="D5" t="n">
-        <v>383179900</v>
+        <v>210000000</v>
       </c>
       <c r="E5" t="n">
-        <v>-71282838</v>
+        <v>-152353577</v>
       </c>
       <c r="F5" t="n">
-        <v>297552618</v>
+        <v>183884753</v>
       </c>
       <c r="G5" t="n">
-        <v>511834079</v>
+        <v>202617643</v>
       </c>
       <c r="H5" t="n">
-        <v>-6163166</v>
+        <v>530452</v>
       </c>
       <c r="I5" t="n">
-        <v>-208118295</v>
+        <v>-19263342</v>
       </c>
       <c r="J5" t="n">
-        <v>-142332680</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-148771500</v>
-      </c>
+        <v>-77974128</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-148771500</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>7219900</v>
+        <v>-77000000</v>
       </c>
       <c r="N5" t="n">
-        <v>7219900</v>
+        <v>-77000000</v>
       </c>
       <c r="O5" t="n">
-        <v>-375960000</v>
+        <v>-287000000</v>
       </c>
       <c r="P5" t="n">
-        <v>383179900</v>
+        <v>210000000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-137538236</v>
-      </c>
-      <c r="R5" t="n">
-        <v>-66400000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-66400000</v>
-      </c>
+        <v>-117901950</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>-71138236</v>
+        <v>-117901950</v>
       </c>
       <c r="U5" t="n">
-        <v>144602</v>
+        <v>34451627</v>
       </c>
       <c r="V5" t="n">
-        <v>-71282838</v>
+        <v>-152353577</v>
       </c>
       <c r="W5" t="n">
-        <v>71752621</v>
+        <v>176612736</v>
       </c>
       <c r="X5" t="n">
-        <v>-27527078</v>
+        <v>-19646077</v>
       </c>
       <c r="Y5" t="n">
-        <v>-31633475</v>
+        <v>-21695280</v>
       </c>
       <c r="Z5" t="n">
-        <v>-94702346</v>
+        <v>-112651602</v>
       </c>
       <c r="AA5" t="n">
-        <v>26411143</v>
+        <v>-17580471</v>
       </c>
       <c r="AB5" t="n">
-        <v>-44656870</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>72784666</v>
-      </c>
+        <v>-103269963</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>43141</v>
+        <v>725409</v>
       </c>
       <c r="AE5" t="n">
-        <v>-149284426</v>
+        <v>7473423</v>
       </c>
       <c r="AF5" t="n">
-        <v>28048230</v>
+        <v>18476621</v>
       </c>
       <c r="AG5" t="n">
-        <v>66400000</v>
+        <v>3078422</v>
       </c>
       <c r="AH5" t="n">
-        <v>116994585</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>612573</v>
-      </c>
+        <v>121680515</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>116382012</v>
+        <v>121680515</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1618</v>
+        <v>-120549</v>
       </c>
       <c r="AL5" t="n">
-        <v>363365</v>
+        <v>-9854029</v>
       </c>
       <c r="AM5" t="n">
-        <v>14118021</v>
+        <v>159453279</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>146900356</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-446000000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>260000000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-128028384</v>
+      </c>
+      <c r="F6" t="n">
+        <v>150038542</v>
+      </c>
+      <c r="G6" t="n">
+        <v>183884753</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-890323</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-32955888</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-186875868</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>-186000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-186000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-446000000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>260000000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-121008760</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>-121008760</v>
+      </c>
+      <c r="U6" t="n">
+        <v>7019624</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-128028384</v>
+      </c>
+      <c r="W6" t="n">
+        <v>274928740</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-15120687</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-14290096</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-80432480</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>4934793</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>40699185</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
+        <v>-18196</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-126048262</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12923017</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>4352360</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>119647768</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>119647768</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>70585</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>4328020</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>201787813</v>
       </c>
     </row>
   </sheetData>
@@ -3501,197 +3665,197 @@
       </c>
       <c r="CW1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>ipoExpectedDate</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>ipoExpectedDate</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EJ1" t="inlineStr">
@@ -3789,64 +3953,64 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.698</v>
+        <v>1.686</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>6.9999995</v>
       </c>
       <c r="AE2" t="n">
-        <v>2000</v>
+        <v>96000</v>
       </c>
       <c r="AF2" t="n">
-        <v>2000</v>
+        <v>96000</v>
       </c>
       <c r="AG2" t="n">
-        <v>757900</v>
+        <v>458766</v>
       </c>
       <c r="AH2" t="n">
-        <v>227800</v>
+        <v>299800</v>
       </c>
       <c r="AI2" t="n">
-        <v>227800</v>
+        <v>299800</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="AL2" t="n">
-        <v>1440000000</v>
+        <v>1260000000</v>
       </c>
       <c r="AM2" t="n">
-        <v>1428000000</v>
+        <v>1260000000</v>
       </c>
       <c r="AN2" t="n">
         <v>0.435</v>
@@ -3861,13 +4025,13 @@
         <v>0.285</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.94172025</v>
+        <v>0.8240052</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.3024</v>
+        <v>1.2404</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.04905</v>
+        <v>1.0802</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -3884,7 +4048,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>1470905344</v>
+        <v>1386905344</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.102189995</v>
@@ -3905,10 +4069,10 @@
         <v>1200000000</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.7341866</v>
+        <v>1.7339135</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.69196707</v>
+        <v>0.6055665</v>
       </c>
       <c r="BH2" t="n">
         <v>1767139200</v>
@@ -3929,16 +4093,16 @@
         <v>0.15</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.962</v>
+        <v>0.907</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.888</v>
+        <v>3.666</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.5052631</v>
+        <v>1.1875</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -3946,7 +4110,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -4050,153 +4214,153 @@
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
+          <t>China Gas Industry Investment Holdings Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="CX2" t="n">
+        <v>-3.669732</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>1756465140</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1757073600</v>
+      </c>
+      <c r="DB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.1904</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.15349887</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0.030200005</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.027957791</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>2020-12-21</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>China Gas Industry Investment Holdings Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CX2" t="n">
-        <v>1780453176</v>
-      </c>
-      <c r="CY2" t="inlineStr">
+      <c r="DO2" t="n">
+        <v>1781765030</v>
+      </c>
+      <c r="DP2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>finmb_33804333</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DR2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
+      <c r="DS2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DC2" t="n">
+      <c r="DT2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DE2" t="b">
+      <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>China Gas Industry Investment Holdings Co. Ltd.</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DW2" t="inlineStr">
         <is>
           <t>CGII HLDGS</t>
         </is>
       </c>
-      <c r="DH2" t="b">
+      <c r="DX2" t="b">
         <v>0</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DY2" t="n">
         <v>1609205400000</v>
       </c>
-      <c r="DJ2" t="n">
-        <v>0.00999999</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>1.2 - 1.2</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DZ2" t="n">
+        <v>-0.04000008</v>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>1.03 - 1.06</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DM2" t="n">
-        <v>757900</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.76500005</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1.7586207</v>
-      </c>
-      <c r="DP2" t="inlineStr">
+      <c r="EC2" t="n">
+        <v>458766</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.61499995</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>1.413793</v>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>0.435 - 2.0</t>
         </is>
       </c>
-      <c r="DQ2" t="n">
-        <v>-0.79999995</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.39999998</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>150.5263</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1756465140</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1757073600</v>
-      </c>
-      <c r="DV2" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.102399945</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.07862404000000001</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.15095007</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>0.14389217</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>2020-12-21</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>China Gas Industry Investment Holdings Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EG2" t="b">
-        <v>0</v>
+      <c r="EG2" t="n">
+        <v>-0.95000005</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.8403353</v>
+        <v>-0.47500002</v>
       </c>
       <c r="EI2" t="n">
-        <v>1.2</v>
+        <v>118.75</v>
       </c>
       <c r="EJ2" t="inlineStr"/>
     </row>
